--- a/Templates/bulkImport/config/construct_SDL_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_SDL_config_sabah.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
-    <sheet name="construct_SDL_config_sabah" sheetId="1" r:id="rId4"/>
+    <sheet name="construct_SDL_config_sabah" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>*</t>
   </si>
@@ -38,21 +50,42 @@
     <t>c_weather_2</t>
   </si>
   <si>
+    <t>c_manpower</t>
+  </si>
+  <si>
     <t>c_total_manpower</t>
   </si>
   <si>
+    <t>c_machinery</t>
+  </si>
+  <si>
     <t>c_total_machinery</t>
   </si>
   <si>
-    <t>c_site_activities</t>
-  </si>
-  <si>
-    <t>c_test</t>
+    <t>c_site_activities_v2</t>
+  </si>
+  <si>
+    <t>c_test_v2</t>
   </si>
   <si>
     <t>c_file</t>
   </si>
   <si>
+    <t>c_contractor_remarks</t>
+  </si>
+  <si>
+    <t>c_contractor_name</t>
+  </si>
+  <si>
+    <t>c_contractor_date</t>
+  </si>
+  <si>
+    <t>c_contractor_designation</t>
+  </si>
+  <si>
+    <t>c_contractor_company</t>
+  </si>
+  <si>
     <t>c_actioner</t>
   </si>
   <si>
@@ -62,6 +95,57 @@
     <t>c_action_status</t>
   </si>
   <si>
+    <t>c_action_date</t>
+  </si>
+  <si>
+    <t>c_sdl_action</t>
+  </si>
+  <si>
+    <t>c_acknowledger_name</t>
+  </si>
+  <si>
+    <t>c_acknowledge_position</t>
+  </si>
+  <si>
+    <t>c_acknowledger_company</t>
+  </si>
+  <si>
+    <t>c_acknowledged_time</t>
+  </si>
+  <si>
+    <t>c_acknowledged_date</t>
+  </si>
+  <si>
+    <t>c_acknowlegde_file</t>
+  </si>
+  <si>
+    <t>c_acknowledge_remarks</t>
+  </si>
+  <si>
+    <t>c_verification_remarks</t>
+  </si>
+  <si>
+    <t>c_verification_attachment</t>
+  </si>
+  <si>
+    <t>c_verify_name</t>
+  </si>
+  <si>
+    <t>c_verify_date</t>
+  </si>
+  <si>
+    <t>c_close_by</t>
+  </si>
+  <si>
+    <t>c_close_date</t>
+  </si>
+  <si>
+    <t>c_sdl_CloseRemarks</t>
+  </si>
+  <si>
+    <t>c_close_attachment</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -80,9 +164,15 @@
     <t>Manpower</t>
   </si>
   <si>
+    <t>Total Manpower</t>
+  </si>
+  <si>
     <t>Plant &amp; Machinery</t>
   </si>
   <si>
+    <t>Total Machinery</t>
+  </si>
+  <si>
     <t>Site Activities / Work Descriptions</t>
   </si>
   <si>
@@ -92,6 +182,18 @@
     <t>Attachment(s)</t>
   </si>
   <si>
+    <t>Remarks - Contractor</t>
+  </si>
+  <si>
+    <t>Recorded By</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
     <t>Actioner</t>
   </si>
   <si>
@@ -99,54 +201,725 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Action Date</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Acknowledge Remarks</t>
+  </si>
+  <si>
+    <t>Verification Remarks</t>
+  </si>
+  <si>
+    <t>Name (Verified)</t>
+  </si>
+  <si>
+    <t>Date Verified</t>
+  </si>
+  <si>
+    <t>Name (Closed)</t>
+  </si>
+  <si>
+    <t>Closed Date</t>
+  </si>
+  <si>
+    <t>Close Remarks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -431,220 +1204,505 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AK5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="true" style="0"/>
-    <col min="2" max="2" width="13.88671875" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.33203125" customWidth="true" style="0"/>
-    <col min="4" max="4" width="18.109375" customWidth="true" style="0"/>
-    <col min="5" max="5" width="18.109375" customWidth="true" style="0"/>
-    <col min="6" max="6" width="17.88671875" customWidth="true" style="0"/>
-    <col min="7" max="7" width="17.5546875" customWidth="true" style="0"/>
-    <col min="8" max="8" width="15.33203125" customWidth="true" style="0"/>
-    <col min="9" max="9" width="18.6640625" customWidth="true" style="0"/>
-    <col min="10" max="10" width="5.88671875" customWidth="true" style="0"/>
-    <col min="11" max="11" width="21.88671875" customWidth="true" style="0"/>
-    <col min="12" max="12" width="21.88671875" customWidth="true" style="0"/>
-    <col min="13" max="13" width="6.44140625" customWidth="true" style="0"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8888888888889" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.2222222222222" style="1" customWidth="1"/>
+    <col min="7" max="8" width="18.1111111111111" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7777777777778" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.4444444444444" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.7777777777778" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7777777777778" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.7777777777778" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.1111111111111" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10.4444444444444" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.1111111111111" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.7777777777778" style="1" customWidth="1"/>
+    <col min="22" max="22" width="12.1111111111111" style="1" customWidth="1"/>
+    <col min="23" max="23" width="20.4444444444444" style="1" customWidth="1"/>
+    <col min="24" max="24" width="21.8888888888889" style="1" customWidth="1"/>
+    <col min="25" max="25" width="23.5555555555556" style="1" customWidth="1"/>
+    <col min="26" max="26" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.7777777777778" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4444444444444" style="1" customWidth="1"/>
+    <col min="29" max="29" width="21.8888888888889" style="1" customWidth="1"/>
+    <col min="30" max="30" width="20.4444444444444" style="1" customWidth="1"/>
+    <col min="31" max="31" width="23.4444444444444" style="1" customWidth="1"/>
+    <col min="32" max="32" width="15" style="1" customWidth="1"/>
+    <col min="33" max="33" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="34" max="34" width="14" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7777777777778" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.1111111111111" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
+    <row r="2" spans="1:37">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3">
+    <row r="3" spans="1:37">
+      <c r="A3" s="1">
         <v>0</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>6</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>7</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>8</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>9</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>10</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>11</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>12</v>
       </c>
+      <c r="N3" s="1">
+        <v>13</v>
+      </c>
+      <c r="O3" s="1">
+        <v>14</v>
+      </c>
+      <c r="P3" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>16</v>
+      </c>
+      <c r="R3" s="1">
+        <v>17</v>
+      </c>
+      <c r="S3" s="1">
+        <v>18</v>
+      </c>
+      <c r="T3" s="1">
+        <v>19</v>
+      </c>
+      <c r="U3" s="1">
+        <v>20</v>
+      </c>
+      <c r="V3" s="1">
+        <v>21</v>
+      </c>
+      <c r="W3" s="1">
+        <v>22</v>
+      </c>
+      <c r="X3" s="1">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>32</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>33</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>34</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>35</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
+    <row r="4" spans="1:37">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="N4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>27</v>
+    <row r="5" spans="1:37">
+      <c r="A5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>